--- a/artfynd/A 37591-2023 artfynd.xlsx
+++ b/artfynd/A 37591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325462</v>
       </c>
       <c r="B2" t="n">
-        <v>99148</v>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37591-2023 artfynd.xlsx
+++ b/artfynd/A 37591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325462</v>
       </c>
       <c r="B2" t="n">
-        <v>99153</v>
+        <v>99246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37591-2023 artfynd.xlsx
+++ b/artfynd/A 37591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325462</v>
       </c>
       <c r="B2" t="n">
-        <v>99246</v>
+        <v>99260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37591-2023 artfynd.xlsx
+++ b/artfynd/A 37591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325462</v>
       </c>
       <c r="B2" t="n">
-        <v>99260</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37591-2023 artfynd.xlsx
+++ b/artfynd/A 37591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325462</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37591-2023 artfynd.xlsx
+++ b/artfynd/A 37591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325462</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37591-2023 artfynd.xlsx
+++ b/artfynd/A 37591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325462</v>
       </c>
       <c r="B2" t="n">
-        <v>99269</v>
+        <v>99296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37591-2023 artfynd.xlsx
+++ b/artfynd/A 37591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325462</v>
       </c>
       <c r="B2" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37591-2023 artfynd.xlsx
+++ b/artfynd/A 37591-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325462</v>
       </c>
       <c r="B2" t="n">
-        <v>99309</v>
+        <v>99313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37591-2023 artfynd.xlsx
+++ b/artfynd/A 37591-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128325462</v>
+        <v>54612216</v>
       </c>
       <c r="B2" t="n">
-        <v>99313</v>
+        <v>56896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222322</v>
+        <v>100089</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Gotlandssnok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Natrix natrix gotlandica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>Nilson &amp; Andrén, 1981</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Artrik vägkant, Gtl</t>
+          <t>Hau träsk, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736699</v>
+        <v>736881</v>
       </c>
       <c r="R2" t="n">
-        <v>6424417</v>
+        <v>6424263</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>södraDBDennis Nyström</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,15 +773,337 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Sixten Anna Johansson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Sixten Anna Johansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>72871175</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hau, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>736451</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6424219</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fleringe</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-06-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>88439128</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103647</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221978</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bergjohannesört</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>hau träsk, Hau, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>736787</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6424168</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fleringe</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elina  Ambjörnsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128325462</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99803</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>736699</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6424417</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fleringe</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>södraDBDennis Nyström</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Via Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 37591-2023 artfynd.xlsx
+++ b/artfynd/A 37591-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72871175</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54612216</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88439128</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,8 +1128,19 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128325462</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>